--- a/工业企业整治测试.xlsx
+++ b/工业企业整治测试.xlsx
@@ -74,7 +74,7 @@
     <t>先正达（苏州）作物保护有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业废水接纳整治\先正达（苏州）作物保护有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业废水接纳整治\先正达（苏州）作物保护有限公司.pdf</t>
   </si>
   <si>
     <t>da35843e5f2c025b0e5e9af86fa50075</t>
@@ -86,7 +86,7 @@
     <t>昆山迈高工业地产开发有限公司（曼胡默尔）.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业废水接纳整治\昆山迈高工业地产开发有限公司（曼胡默尔）.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业废水接纳整治\昆山迈高工业地产开发有限公司（曼胡默尔）.pdf</t>
   </si>
   <si>
     <t>fa42aafbd0f079a2f7bef9ce001ed224</t>
@@ -101,7 +101,7 @@
     <t>华达利家具( 中国)有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\华达利家具( 中国)有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\华达利家具( 中国)有限公司.pdf</t>
   </si>
   <si>
     <t>4b4d66f3ed224c79ea5a725253f2e9b1</t>
@@ -113,7 +113,7 @@
     <t>启佳通讯（昆山）有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\启佳通讯（昆山）有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\启佳通讯（昆山）有限公司.pdf</t>
   </si>
   <si>
     <t>54ba1e3e9ebd5f5be5280d5973dff241</t>
@@ -125,7 +125,7 @@
     <t>启基永昌通讯（昆山）有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\启基永昌通讯（昆山）有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\启基永昌通讯（昆山）有限公司.pdf</t>
   </si>
   <si>
     <t>bc7d6c95d7d2f6bb03106b453a03e3ac</t>
@@ -137,7 +137,7 @@
     <t>坚田电机（昆山）有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\坚田电机（昆山）有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\坚田电机（昆山）有限公司.pdf</t>
   </si>
   <si>
     <t>c7b1745cd451d7e248ed051490cb0991</t>
@@ -149,7 +149,7 @@
     <t>新格五金工业（昆山）有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\新格五金工业（昆山）有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\新格五金工业（昆山）有限公司.pdf</t>
   </si>
   <si>
     <t>7d4e3e69e3e5e715aa8121f76af121a6</t>
@@ -161,7 +161,7 @@
     <t>昆山之富士机械制造有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山之富士机械制造有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山之富士机械制造有限公司.pdf</t>
   </si>
   <si>
     <t>468c9d71f3b352d2164debf85a0daea4</t>
@@ -173,7 +173,7 @@
     <t>昆山乾坤机器制造有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山乾坤机器制造有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山乾坤机器制造有限公司.pdf</t>
   </si>
   <si>
     <t>cbe1e66330e580d377d7ffe45a769244</t>
@@ -185,7 +185,7 @@
     <t>昆山伯根大通自动化技术有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山伯根大通自动化技术有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山伯根大通自动化技术有限公司.pdf</t>
   </si>
   <si>
     <t>9d8f1fb8ee6c8a51615e1618826b6336</t>
@@ -197,7 +197,7 @@
     <t>昆山倍力扣金属制品有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山倍力扣金属制品有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山倍力扣金属制品有限公司.pdf</t>
   </si>
   <si>
     <t>22e4b5743fb19d43a9a5a757dda1d29f</t>
@@ -209,7 +209,7 @@
     <t>昆山嘉隆模具钢材有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山嘉隆模具钢材有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山嘉隆模具钢材有限公司.pdf</t>
   </si>
   <si>
     <t>3ffdec8d8c2beaf79576f4bebcd04c54</t>
@@ -221,7 +221,7 @@
     <t>昆山市峰根豪饮料厂.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山市峰根豪饮料厂.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山市峰根豪饮料厂.pdf</t>
   </si>
   <si>
     <t>7b827ed0162541b624b17fb533ee3cbd</t>
@@ -233,7 +233,7 @@
     <t>昆山市广进经贸有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山市广进经贸有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山市广进经贸有限公司.pdf</t>
   </si>
   <si>
     <t>91d34b912e17be4987fc57fc95a36593</t>
@@ -245,7 +245,7 @@
     <t>昆山市禾顺砂布纸有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山市禾顺砂布纸有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山市禾顺砂布纸有限公司.pdf</t>
   </si>
   <si>
     <t>7ffff03209ad893c9ca215eb88f1187a</t>
@@ -257,7 +257,7 @@
     <t>昆山市荣华五金厂.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山市荣华五金厂.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山市荣华五金厂.pdf</t>
   </si>
   <si>
     <t>68f2a13876556373ec168712876b25e5</t>
@@ -269,7 +269,7 @@
     <t>昆山市豫昆运输有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山市豫昆运输有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山市豫昆运输有限公司.pdf</t>
   </si>
   <si>
     <t>24ee17b541edaaaa0b6243d8088cab24</t>
@@ -281,7 +281,7 @@
     <t>昆山市金洋五金厂.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山市金洋五金厂.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山市金洋五金厂.pdf</t>
   </si>
   <si>
     <t>3e84f2f0b3323963e80140de7d22da59</t>
@@ -293,7 +293,7 @@
     <t>昆山市鑫健金属制品有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山市鑫健金属制品有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山市鑫健金属制品有限公司.pdf</t>
   </si>
   <si>
     <t>af2a6636cdbebba99ba45a3660e8298d</t>
@@ -305,7 +305,7 @@
     <t>昆山开发区东发食品有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山开发区东发食品有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山开发区东发食品有限公司.pdf</t>
   </si>
   <si>
     <t>5193f87c63718bd05d6196e103e85d94</t>
@@ -317,7 +317,7 @@
     <t>昆山无水港国际物流发展有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山无水港国际物流发展有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山无水港国际物流发展有限公司.pdf</t>
   </si>
   <si>
     <t>757e77bf9b64a81ed62690d4df6f6292</t>
@@ -329,7 +329,7 @@
     <t>昆山泉宏五金机械有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山泉宏五金机械有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山泉宏五金机械有限公司.pdf</t>
   </si>
   <si>
     <t>73dc63b1de5a5cd9cd80cea8ecaab542</t>
@@ -341,7 +341,7 @@
     <t>昆山海圳汽车技术发展有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山海圳汽车技术发展有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山海圳汽车技术发展有限公司.pdf</t>
   </si>
   <si>
     <t>2ff6d5e077122e72d2e0be23a5515bef</t>
@@ -353,7 +353,7 @@
     <t>昆山联华精密机械制造有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山联华精密机械制造有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\昆山联华精密机械制造有限公司.pdf</t>
   </si>
   <si>
     <t>51f398607aeea2193a0a2ff49025a758</t>
@@ -365,7 +365,7 @@
     <t>显亮(昆山）汽车配件有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\显亮(昆山）汽车配件有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\显亮(昆山）汽车配件有限公司.pdf</t>
   </si>
   <si>
     <t>fa4d3287ecc28b807257a6f15b238ee5</t>
@@ -377,7 +377,7 @@
     <t>江苏雷特电机股份有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\江苏雷特电机股份有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\江苏雷特电机股份有限公司.pdf</t>
   </si>
   <si>
     <t>3314a5b0b63f0eb0bd712e99087a81d9</t>
@@ -389,7 +389,7 @@
     <t>维乐车料（昆山）有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\维乐车料（昆山）有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\维乐车料（昆山）有限公司.pdf</t>
   </si>
   <si>
     <t>5a289bdc20cd6c7b07985c30853d4bab</t>
@@ -401,7 +401,7 @@
     <t>美昌科技（昆山）有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\美昌科技（昆山）有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\美昌科技（昆山）有限公司.pdf</t>
   </si>
   <si>
     <t>004e91d1bb3f42144ad877ee05b0d84b</t>
@@ -413,7 +413,7 @@
     <t>苏州崇隆电子科技有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\苏州崇隆电子科技有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\苏州崇隆电子科技有限公司.pdf</t>
   </si>
   <si>
     <t>1531990db3ad0b1bcd82ad4e01d03dd0</t>
@@ -425,7 +425,7 @@
     <t>英惠印刷（昆山）有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\英惠印刷（昆山）有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\英惠印刷（昆山）有限公司.pdf</t>
   </si>
   <si>
     <t>41340a1f390bb57b26c5ff7f08d48101</t>
@@ -437,7 +437,7 @@
     <t>荣轮机械（昆山）有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\荣轮机械（昆山）有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\荣轮机械（昆山）有限公司.pdf</t>
   </si>
   <si>
     <t>3573878cf89a7576079b08f8020c19bc</t>
@@ -449,7 +449,7 @@
     <t>麦迪实软件(昆山)有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\麦迪实软件(昆山)有限公司.pdf</t>
+    <t>D:\开发区2022-2024\“333”行动进展情况明细表20232024\工业企业雨污分流\麦迪实软件(昆山)有限公司.pdf</t>
   </si>
   <si>
     <t>541a21d08ccce36469d7a584fa7b0c66</t>
@@ -464,7 +464,7 @@
     <t>昆山旭创电子科技有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业废水接纳整治\昆山旭创电子科技有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业废水接纳整治\昆山旭创电子科技有限公司.pdf</t>
   </si>
   <si>
     <t>29c61b6806be75d6e7ea623f80ac6973</t>
@@ -476,7 +476,7 @@
     <t>昆山龙灯瑞迪制药有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业废水接纳整治\昆山龙灯瑞迪制药有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业废水接纳整治\昆山龙灯瑞迪制药有限公司.pdf</t>
   </si>
   <si>
     <t>1bb1000a39710f18b3dcac36ff3c04ad</t>
@@ -488,7 +488,7 @@
     <t>星巴克（昆山）咖啡有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业废水接纳整治\星巴克（昆山）咖啡有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业废水接纳整治\星巴克（昆山）咖啡有限公司.pdf</t>
   </si>
   <si>
     <t>96e0fecc0990b8d7ee7e2a38ffb987a1</t>
@@ -500,7 +500,7 @@
     <t>泰瑞美（昆山）精密科技有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业废水接纳整治\泰瑞美（昆山）精密科技有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业废水接纳整治\泰瑞美（昆山）精密科技有限公司.pdf</t>
   </si>
   <si>
     <t>d52292a8e15cb37cc0ffc789bcb1d42c</t>
@@ -512,7 +512,7 @@
     <t>翊腾电子科技（昆山）有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业废水接纳整治\翊腾电子科技（昆山）有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业废水接纳整治\翊腾电子科技（昆山）有限公司.pdf</t>
   </si>
   <si>
     <t>ac1d23b618bd6b24587c85db38f1fa18</t>
@@ -524,13 +524,13 @@
     <t>六丰模具（昆山）有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\六丰模具（昆山）有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\六丰模具（昆山）有限公司.pdf</t>
   </si>
   <si>
     <t>deb8d9e9f5831a118c20b33cbe099b02</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\华达利家具( 中国)有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\华达利家具( 中国)有限公司.pdf</t>
   </si>
   <si>
     <t>55d6a72455b448e360fcafc6975bddef</t>
@@ -542,7 +542,7 @@
     <t>嘉浦薄膜新材料（昆山）有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\嘉浦薄膜新材料（昆山）有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\嘉浦薄膜新材料（昆山）有限公司.pdf</t>
   </si>
   <si>
     <t>c1ef06c0b3fd863b8cddd26e21d88894</t>
@@ -554,7 +554,7 @@
     <t>新华电子零件（昆山）有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\新华电子零件（昆山）有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\新华电子零件（昆山）有限公司.pdf</t>
   </si>
   <si>
     <t>be6ffb934773024a25e7664008ab3631</t>
@@ -566,7 +566,7 @@
     <t>昆山元生华成汽车销售服务有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山元生华成汽车销售服务有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山元生华成汽车销售服务有限公司.pdf</t>
   </si>
   <si>
     <t>4ba9013267cd0f827a44b368c1991cf3</t>
@@ -578,7 +578,7 @@
     <t>昆山华恒焊接股份有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山华恒焊接股份有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山华恒焊接股份有限公司.pdf</t>
   </si>
   <si>
     <t>9a0f88a75251db3f761396ad7dbe5785</t>
@@ -590,7 +590,7 @@
     <t>昆山华阳新材料股份有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山华阳新材料股份有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山华阳新材料股份有限公司.pdf</t>
   </si>
   <si>
     <t>bc4cc07e78f5b76c0fb5744af875485d</t>
@@ -602,7 +602,7 @@
     <t>昆山南方昊塑料制品有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山南方昊塑料制品有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山南方昊塑料制品有限公司.pdf</t>
   </si>
   <si>
     <t>3bfbca11b3f61b396aa20cd7662ab886</t>
@@ -614,7 +614,7 @@
     <t>昆山叶新机械制造有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山叶新机械制造有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山叶新机械制造有限公司.pdf</t>
   </si>
   <si>
     <t>8352ae92911c8c4f4b07c875cd949a9c</t>
@@ -626,7 +626,7 @@
     <t>昆山君合光电器件有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山君合光电器件有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山君合光电器件有限公司.pdf</t>
   </si>
   <si>
     <t>1fabf15a22d10e838946cb4a363ffc05</t>
@@ -638,7 +638,7 @@
     <t>昆山复盛运动用品有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山复盛运动用品有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山复盛运动用品有限公司.pdf</t>
   </si>
   <si>
     <t>f7358007638e05a3c7aaa36bb6528644</t>
@@ -650,7 +650,7 @@
     <t>昆山奕诚贸易有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山奕诚贸易有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山奕诚贸易有限公司.pdf</t>
   </si>
   <si>
     <t>4aaff6fa906e567d65ffc199dfc523d7</t>
@@ -662,7 +662,7 @@
     <t>昆山市周市申飞包装箱厂.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市周市申飞包装箱厂.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市周市申飞包装箱厂.pdf</t>
   </si>
   <si>
     <t>c5fd398b8cd6a9618763ab9233ea2652</t>
@@ -674,7 +674,7 @@
     <t>昆山市天溢包装有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市天溢包装有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市天溢包装有限公司.pdf</t>
   </si>
   <si>
     <t>8878ad9a09853cfdce82d025ba8b40e2</t>
@@ -686,7 +686,7 @@
     <t>昆山市惠生金属容器再生有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市惠生金属容器再生有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市惠生金属容器再生有限公司.pdf</t>
   </si>
   <si>
     <t>e0e5cca60af89123117ef6efa782f95a</t>
@@ -698,7 +698,7 @@
     <t>昆山市振兴金属制品厂.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市振兴金属制品厂.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市振兴金属制品厂.pdf</t>
   </si>
   <si>
     <t>af567502955c17be6dbf4c485f6e1e53</t>
@@ -710,7 +710,7 @@
     <t>昆山市申飞五金厂.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市申飞五金厂.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市申飞五金厂.pdf</t>
   </si>
   <si>
     <t>a049636ea159b16a4edb3572d2205f0f</t>
@@ -722,7 +722,7 @@
     <t>昆山市荣乐冷却机械设备有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市荣乐冷却机械设备有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市荣乐冷却机械设备有限公司.pdf</t>
   </si>
   <si>
     <t>1f5949572f3ebf2e0326b3c0db651d40</t>
@@ -734,7 +734,7 @@
     <t>昆山市银茂精密模具厂.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市银茂精密模具厂.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市银茂精密模具厂.pdf</t>
   </si>
   <si>
     <t>036e352507b40828a80152bb170b6cde</t>
@@ -746,7 +746,7 @@
     <t>昆山市青阳物业管理中心.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市青阳物业管理中心.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山市青阳物业管理中心.pdf</t>
   </si>
   <si>
     <t>9ae2f6ebd8a1a6bae749096f8c00965f</t>
@@ -758,7 +758,7 @@
     <t>昆山新联纺针织有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山新联纺针织有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山新联纺针织有限公司.pdf</t>
   </si>
   <si>
     <t>8099559fe36677c900c64b475105ca4f</t>
@@ -770,7 +770,7 @@
     <t>昆山明易汽车饰件有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山明易汽车饰件有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山明易汽车饰件有限公司.pdf</t>
   </si>
   <si>
     <t>d237db44d40c18f5401ca1bb0c593d27</t>
@@ -782,7 +782,7 @@
     <t>昆山永兴建材有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山永兴建材有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山永兴建材有限公司.pdf</t>
   </si>
   <si>
     <t>c75e14e87055dd5f7603184c0f2ff839</t>
@@ -794,7 +794,7 @@
     <t>昆山浩兴电子科技有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山浩兴电子科技有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山浩兴电子科技有限公司.pdf</t>
   </si>
   <si>
     <t>92e6dc35ea7e147b169e569ccfa5c0cd</t>
@@ -806,7 +806,7 @@
     <t>昆山盛达汽车销售服务有限公司维修分公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山盛达汽车销售服务有限公司维修分公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\昆山盛达汽车销售服务有限公司维修分公司.pdf</t>
   </si>
   <si>
     <t>8129897e97cfc0cf6c5605412b3a6d91</t>
@@ -818,7 +818,7 @@
     <t>江苏正业智造技术有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\江苏正业智造技术有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\江苏正业智造技术有限公司.pdf</t>
   </si>
   <si>
     <t>45e073c8addacb0cc8b4599741c71879</t>
@@ -830,7 +830,7 @@
     <t>江苏联鑫电子工业有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\江苏联鑫电子工业有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\江苏联鑫电子工业有限公司.pdf</t>
   </si>
   <si>
     <t>65a682faa32009114ed5bf66366cac78</t>
@@ -842,7 +842,7 @@
     <t>江苏阳澄电力建设有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\江苏阳澄电力建设有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\江苏阳澄电力建设有限公司.pdf</t>
   </si>
   <si>
     <t>caf0ddc49473e58e8b138be5c3d6b783</t>
@@ -854,7 +854,7 @@
     <t>立臻科技（昆山）有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\立臻科技（昆山）有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\立臻科技（昆山）有限公司.pdf</t>
   </si>
   <si>
     <t>6761cb2e5a04e3e35d20f030d65000d3</t>
@@ -866,7 +866,7 @@
     <t>竞陆电子（昆山）有限公司.pdf</t>
   </si>
   <si>
-    <t>E:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\竞陆电子（昆山）有限公司.pdf</t>
+    <t>D:\开发区2022-2024\开发区2023年333资料\工业企业雨污分流\竞陆电子（昆山）有限公司.pdf</t>
   </si>
   <si>
     <t>a031e63e173ed2d1834333f88df12072</t>
